--- a/docs/Logic Requirements/Ageipelago Alaric.xlsx
+++ b/docs/Logic Requirements/Ageipelago Alaric.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BCAB41-9773-464E-9C60-D333312FDC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80780339-29E1-4CF8-B363-5C72F5A980DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="188">
   <si>
     <t>Scenario</t>
   </si>
@@ -3319,12 +3319,71 @@
 (Despawns in Vanilla)</t>
     </r>
   </si>
+  <si>
+    <t>Restrictions</t>
+  </si>
+  <si>
+    <t>Castle - Imperial Age</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Technologies</t>
+  </si>
+  <si>
+    <t>Unrestricted</t>
+  </si>
+  <si>
+    <t>Castle Age</t>
+  </si>
+  <si>
+    <t>Goths Cannot build Stone Walls, Stone Gates, Fortified Walls or Fortified Gates</t>
+  </si>
+  <si>
+    <t>Unavailable</t>
+  </si>
+  <si>
+    <t>No Trade Cart
+No Villager
+No Fishing Ship
+No Transport Ship
+No Fire Galley
+No Galley
+No Hulk
+No Demolition Raft
+No Trade Cog</t>
+  </si>
+  <si>
+    <t>Anarchy is researched automaticaly
+No Caravan
+No Careening
+No Clinker Construction
+No Siphons
+No Hand Cart
+No Town Patrol
+No Medium Warships
+No Gillnets
+No Bow Saw
+No Heavy Plow
+No Stone Shaft Mining</t>
+  </si>
+  <si>
+    <t>No Bombard Cannon
+No Hand Cannoneer</t>
+  </si>
+  <si>
+    <t>Imperial Age</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3492,6 +3551,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3501,7 +3567,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -3637,11 +3703,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3758,6 +3848,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4390,15 +4507,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9316089-FB11-4993-993E-327A61138A4D}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
       <c r="G2" s="2" t="s">
         <v>76</v>
       </c>
@@ -4412,7 +4535,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45"/>
       <c r="G3" s="13" t="s">
         <v>78</v>
       </c>
@@ -4426,7 +4554,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="G4" s="9" t="s">
         <v>123</v>
       </c>
@@ -4440,7 +4577,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>180</v>
+      </c>
       <c r="G5" s="9" t="s">
         <v>83</v>
       </c>
@@ -4454,7 +4600,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="18"/>
       <c r="G6" s="9" t="s">
         <v>81</v>
       </c>
@@ -4468,7 +4617,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="18"/>
       <c r="G7" s="33" t="s">
         <v>124</v>
       </c>
@@ -4482,7 +4634,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="18"/>
       <c r="G8" s="14" t="s">
         <v>103</v>
       </c>
@@ -4496,7 +4651,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="18"/>
       <c r="G9" s="14" t="s">
         <v>88</v>
       </c>
@@ -4510,7 +4668,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="18"/>
       <c r="G10" s="14" t="s">
         <v>120</v>
       </c>
@@ -4524,7 +4685,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="18"/>
       <c r="G11" s="14" t="s">
         <v>125</v>
       </c>
@@ -4538,7 +4702,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="18"/>
       <c r="G12" s="14" t="s">
         <v>126</v>
       </c>
@@ -4552,7 +4719,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="18"/>
       <c r="G13" s="14" t="s">
         <v>127</v>
       </c>
@@ -4566,7 +4736,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="18"/>
       <c r="G14" s="14" t="s">
         <v>105</v>
       </c>
@@ -4580,7 +4753,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="18"/>
       <c r="G15" s="14" t="s">
         <v>96</v>
       </c>
@@ -4594,7 +4770,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="18"/>
       <c r="G16" s="19" t="s">
         <v>86</v>
       </c>
@@ -4791,21 +4970,31 @@
       <c r="L42" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78454FB7-193A-4E5E-9FFF-F84E82675620}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
       <c r="G2" s="2" t="s">
         <v>76</v>
       </c>
@@ -4819,7 +5008,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45"/>
       <c r="G3" s="25" t="s">
         <v>128</v>
       </c>
@@ -4833,7 +5027,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="G4" s="26" t="s">
         <v>120</v>
       </c>
@@ -4847,7 +5050,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="318.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="46" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>185</v>
+      </c>
       <c r="G5" s="26" t="s">
         <v>119</v>
       </c>
@@ -4861,7 +5073,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="18"/>
       <c r="G6" s="26" t="s">
         <v>88</v>
       </c>
@@ -4875,7 +5090,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="18"/>
       <c r="G7" s="15" t="s">
         <v>86</v>
       </c>
@@ -4889,7 +5107,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="18"/>
       <c r="G8" s="15" t="s">
         <v>127</v>
       </c>
@@ -4903,7 +5124,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="18"/>
       <c r="G9" s="15" t="s">
         <v>126</v>
       </c>
@@ -4917,7 +5141,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="18"/>
       <c r="G10" s="27" t="s">
         <v>105</v>
       </c>
@@ -4931,7 +5158,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="18"/>
       <c r="G11" s="27" t="s">
         <v>103</v>
       </c>
@@ -4945,7 +5175,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="18"/>
       <c r="G12" s="27" t="s">
         <v>136</v>
       </c>
@@ -4959,7 +5192,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="18"/>
       <c r="G13" s="14" t="s">
         <v>139</v>
       </c>
@@ -4973,7 +5209,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="18"/>
       <c r="G14" s="14" t="s">
         <v>93</v>
       </c>
@@ -4987,7 +5226,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="18"/>
       <c r="G15" s="28" t="s">
         <v>96</v>
       </c>
@@ -5001,7 +5243,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="18"/>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
       <c r="K16" s="20" t="s">
@@ -5208,21 +5453,31 @@
       <c r="L42" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84100C08-004F-4D07-9790-4EE90877B6D9}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
       <c r="G2" s="2" t="s">
         <v>76</v>
       </c>
@@ -5236,7 +5491,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45"/>
       <c r="G3" s="13" t="s">
         <v>78</v>
       </c>
@@ -5250,7 +5510,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="G4" s="9" t="s">
         <v>83</v>
       </c>
@@ -5264,7 +5533,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>180</v>
+      </c>
       <c r="G5" s="9" t="s">
         <v>81</v>
       </c>
@@ -5278,7 +5556,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="18"/>
       <c r="G6" s="27" t="s">
         <v>90</v>
       </c>
@@ -5292,7 +5573,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="18"/>
       <c r="G7" s="27" t="s">
         <v>86</v>
       </c>
@@ -5306,7 +5590,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="18"/>
       <c r="G8" s="27" t="s">
         <v>120</v>
       </c>
@@ -5320,7 +5607,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="18"/>
       <c r="G9" s="27" t="s">
         <v>127</v>
       </c>
@@ -5334,7 +5624,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="18"/>
       <c r="G10" s="27" t="s">
         <v>105</v>
       </c>
@@ -5348,7 +5641,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="18"/>
       <c r="G11" s="27" t="s">
         <v>96</v>
       </c>
@@ -5362,7 +5658,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="18"/>
       <c r="G12" s="14" t="s">
         <v>136</v>
       </c>
@@ -5376,7 +5675,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="18"/>
       <c r="G13" s="14" t="s">
         <v>126</v>
       </c>
@@ -5390,7 +5692,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="18"/>
       <c r="G14" s="14" t="s">
         <v>119</v>
       </c>
@@ -5404,7 +5709,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="18"/>
       <c r="G15" s="14" t="s">
         <v>138</v>
       </c>
@@ -5418,7 +5726,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="18"/>
       <c r="G16" s="35" t="s">
         <v>115</v>
       </c>
@@ -5725,21 +6036,31 @@
       <c r="L42" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47FF2336-96D8-438B-9597-9B2CCB1DB7A5}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
       <c r="G2" s="2" t="s">
         <v>76</v>
       </c>
@@ -5753,7 +6074,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45"/>
       <c r="G3" s="13" t="s">
         <v>78</v>
       </c>
@@ -5767,7 +6093,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="G4" s="33" t="s">
         <v>160</v>
       </c>
@@ -5781,7 +6116,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>180</v>
+      </c>
       <c r="G5" s="20" t="s">
         <v>148</v>
       </c>
@@ -5795,7 +6139,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="18"/>
       <c r="G6" s="20" t="s">
         <v>149</v>
       </c>
@@ -5809,7 +6156,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="18"/>
       <c r="G7" s="20" t="s">
         <v>105</v>
       </c>
@@ -5823,7 +6173,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="18"/>
       <c r="G8" s="20" t="s">
         <v>126</v>
       </c>
@@ -5837,7 +6190,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="18"/>
       <c r="G9" s="20" t="s">
         <v>88</v>
       </c>
@@ -5851,7 +6207,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="18"/>
       <c r="G10" s="20" t="s">
         <v>119</v>
       </c>
@@ -5865,7 +6224,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="18"/>
       <c r="G11" s="20" t="s">
         <v>127</v>
       </c>
@@ -5879,7 +6241,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="18"/>
       <c r="G12" s="20" t="s">
         <v>103</v>
       </c>
@@ -5893,7 +6258,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="18"/>
       <c r="G13" s="20" t="s">
         <v>125</v>
       </c>
@@ -5907,7 +6275,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="18"/>
       <c r="G14" s="20" t="s">
         <v>145</v>
       </c>
@@ -5921,7 +6292,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="18"/>
       <c r="G15" s="14" t="s">
         <v>161</v>
       </c>
@@ -5935,7 +6309,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="18"/>
       <c r="G16" s="14" t="s">
         <v>138</v>
       </c>
@@ -6182,21 +6559,31 @@
       <c r="L42" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDD0A3DC-2031-4632-A032-6BBB6F614813}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
       <c r="G2" s="2" t="s">
         <v>76</v>
       </c>
@@ -6210,7 +6597,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45"/>
       <c r="G3" s="13" t="s">
         <v>78</v>
       </c>
@@ -6224,7 +6616,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="G4" s="9" t="s">
         <v>123</v>
       </c>
@@ -6238,7 +6639,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>180</v>
+      </c>
       <c r="G5" s="9" t="s">
         <v>83</v>
       </c>
@@ -6252,7 +6662,10 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="18"/>
       <c r="G6" s="15" t="s">
         <v>86</v>
       </c>
@@ -6266,7 +6679,10 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="18"/>
       <c r="G7" s="15" t="s">
         <v>136</v>
       </c>
@@ -6280,7 +6696,10 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="18"/>
       <c r="G8" s="15" t="s">
         <v>103</v>
       </c>
@@ -6294,7 +6713,10 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="18"/>
       <c r="G9" s="15" t="s">
         <v>88</v>
       </c>
@@ -6308,7 +6730,10 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="18"/>
       <c r="G10" s="34" t="s">
         <v>118</v>
       </c>
@@ -6322,7 +6747,10 @@
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="18"/>
       <c r="G11" s="34" t="s">
         <v>166</v>
       </c>
@@ -6336,7 +6764,10 @@
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="18"/>
       <c r="G12" s="15" t="s">
         <v>98</v>
       </c>
@@ -6350,7 +6781,10 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="18"/>
       <c r="G13" s="34" t="s">
         <v>116</v>
       </c>
@@ -6364,7 +6798,10 @@
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="18"/>
       <c r="G14" s="19" t="s">
         <v>127</v>
       </c>
@@ -6378,7 +6815,10 @@
         <v>117</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="18"/>
       <c r="G15" s="19" t="s">
         <v>135</v>
       </c>
@@ -6392,7 +6832,10 @@
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="18"/>
       <c r="G16" s="19" t="s">
         <v>93</v>
       </c>
@@ -6675,6 +7118,10 @@
       <c r="L42" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/Logic Requirements/Ageipelago Alaric.xlsx
+++ b/docs/Logic Requirements/Ageipelago Alaric.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80780339-29E1-4CF8-B363-5C72F5A980DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063FEC41-98DE-432D-AFBC-0CC28231198C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Alaric" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="189">
   <si>
     <t>Scenario</t>
   </si>
@@ -3378,12 +3378,35 @@
   <si>
     <t>Imperial Age</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Standard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+Murder Holes are researched automatically</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3557,6 +3580,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3850,6 +3879,15 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3866,15 +3904,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4517,11 +4546,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="42"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
       <c r="G2" s="2" t="s">
         <v>76</v>
       </c>
@@ -4536,11 +4565,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="45"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
       <c r="G3" s="13" t="s">
         <v>78</v>
       </c>
@@ -4578,14 +4607,14 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="46" t="s">
-        <v>180</v>
+      <c r="D5" s="40" t="s">
+        <v>188</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>83</v>
@@ -4601,8 +4630,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="18"/>
       <c r="G6" s="9" t="s">
         <v>81</v>
@@ -4618,8 +4647,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
       <c r="D7" s="18"/>
       <c r="G7" s="33" t="s">
         <v>124</v>
@@ -4635,8 +4664,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
       <c r="D8" s="18"/>
       <c r="G8" s="14" t="s">
         <v>103</v>
@@ -4652,8 +4681,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
       <c r="D9" s="18"/>
       <c r="G9" s="14" t="s">
         <v>88</v>
@@ -4669,8 +4698,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
       <c r="D10" s="18"/>
       <c r="G10" s="14" t="s">
         <v>120</v>
@@ -4686,8 +4715,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
       <c r="D11" s="18"/>
       <c r="G11" s="14" t="s">
         <v>125</v>
@@ -4703,8 +4732,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
       <c r="D12" s="18"/>
       <c r="G12" s="14" t="s">
         <v>126</v>
@@ -4720,8 +4749,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
       <c r="D13" s="18"/>
       <c r="G13" s="14" t="s">
         <v>127</v>
@@ -4737,8 +4766,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
       <c r="D14" s="18"/>
       <c r="G14" s="14" t="s">
         <v>105</v>
@@ -4754,8 +4783,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="18"/>
       <c r="G15" s="14" t="s">
         <v>96</v>
@@ -4771,8 +4800,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="18"/>
       <c r="G16" s="19" t="s">
         <v>86</v>
@@ -4975,6 +5004,7 @@
     <mergeCell ref="B3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4990,11 +5020,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="42"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
       <c r="G2" s="2" t="s">
         <v>76</v>
       </c>
@@ -5009,11 +5039,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="45"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
       <c r="G3" s="25" t="s">
         <v>128</v>
       </c>
@@ -5051,13 +5081,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="318.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="40" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="40" t="s">
         <v>185</v>
       </c>
       <c r="G5" s="26" t="s">
@@ -5074,8 +5104,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="18"/>
       <c r="G6" s="26" t="s">
         <v>88</v>
@@ -5091,8 +5121,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
       <c r="D7" s="18"/>
       <c r="G7" s="15" t="s">
         <v>86</v>
@@ -5108,8 +5138,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
       <c r="D8" s="18"/>
       <c r="G8" s="15" t="s">
         <v>127</v>
@@ -5125,8 +5155,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
       <c r="D9" s="18"/>
       <c r="G9" s="15" t="s">
         <v>126</v>
@@ -5142,8 +5172,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
       <c r="D10" s="18"/>
       <c r="G10" s="27" t="s">
         <v>105</v>
@@ -5159,8 +5189,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
       <c r="D11" s="18"/>
       <c r="G11" s="27" t="s">
         <v>103</v>
@@ -5176,8 +5206,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
       <c r="D12" s="18"/>
       <c r="G12" s="27" t="s">
         <v>136</v>
@@ -5193,8 +5223,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
       <c r="D13" s="18"/>
       <c r="G13" s="14" t="s">
         <v>139</v>
@@ -5210,8 +5240,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
       <c r="D14" s="18"/>
       <c r="G14" s="14" t="s">
         <v>93</v>
@@ -5227,8 +5257,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="18"/>
       <c r="G15" s="28" t="s">
         <v>96</v>
@@ -5244,8 +5274,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="18"/>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
@@ -5473,11 +5503,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="42"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
       <c r="G2" s="2" t="s">
         <v>76</v>
       </c>
@@ -5492,11 +5522,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="46" t="s">
         <v>176</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="45"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
       <c r="G3" s="13" t="s">
         <v>78</v>
       </c>
@@ -5534,13 +5564,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="40" t="s">
         <v>186</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="40" t="s">
         <v>180</v>
       </c>
       <c r="G5" s="9" t="s">
@@ -5557,8 +5587,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="18"/>
       <c r="G6" s="27" t="s">
         <v>90</v>
@@ -5574,8 +5604,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
       <c r="D7" s="18"/>
       <c r="G7" s="27" t="s">
         <v>86</v>
@@ -5591,8 +5621,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
       <c r="D8" s="18"/>
       <c r="G8" s="27" t="s">
         <v>120</v>
@@ -5608,8 +5638,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
       <c r="D9" s="18"/>
       <c r="G9" s="27" t="s">
         <v>127</v>
@@ -5625,8 +5655,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
       <c r="D10" s="18"/>
       <c r="G10" s="27" t="s">
         <v>105</v>
@@ -5642,8 +5672,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
       <c r="D11" s="18"/>
       <c r="G11" s="27" t="s">
         <v>96</v>
@@ -5659,8 +5689,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
       <c r="D12" s="18"/>
       <c r="G12" s="14" t="s">
         <v>136</v>
@@ -5676,8 +5706,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
       <c r="D13" s="18"/>
       <c r="G13" s="14" t="s">
         <v>126</v>
@@ -5693,8 +5723,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
       <c r="D14" s="18"/>
       <c r="G14" s="14" t="s">
         <v>119</v>
@@ -5710,8 +5740,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="18"/>
       <c r="G15" s="14" t="s">
         <v>138</v>
@@ -5727,8 +5757,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="18"/>
       <c r="G16" s="35" t="s">
         <v>115</v>
@@ -6056,11 +6086,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="42"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
       <c r="G2" s="2" t="s">
         <v>76</v>
       </c>
@@ -6075,11 +6105,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="46" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="45"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
       <c r="G3" s="13" t="s">
         <v>78</v>
       </c>
@@ -6117,13 +6147,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="40" t="s">
         <v>186</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="40" t="s">
         <v>180</v>
       </c>
       <c r="G5" s="20" t="s">
@@ -6140,8 +6170,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="18"/>
       <c r="G6" s="20" t="s">
         <v>149</v>
@@ -6157,8 +6187,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
       <c r="D7" s="18"/>
       <c r="G7" s="20" t="s">
         <v>105</v>
@@ -6174,8 +6204,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
       <c r="D8" s="18"/>
       <c r="G8" s="20" t="s">
         <v>126</v>
@@ -6191,8 +6221,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
       <c r="D9" s="18"/>
       <c r="G9" s="20" t="s">
         <v>88</v>
@@ -6208,8 +6238,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
       <c r="D10" s="18"/>
       <c r="G10" s="20" t="s">
         <v>119</v>
@@ -6225,8 +6255,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
       <c r="D11" s="18"/>
       <c r="G11" s="20" t="s">
         <v>127</v>
@@ -6242,8 +6272,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
       <c r="D12" s="18"/>
       <c r="G12" s="20" t="s">
         <v>103</v>
@@ -6259,8 +6289,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
       <c r="D13" s="18"/>
       <c r="G13" s="20" t="s">
         <v>125</v>
@@ -6276,8 +6306,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
       <c r="D14" s="18"/>
       <c r="G14" s="20" t="s">
         <v>145</v>
@@ -6293,8 +6323,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="18"/>
       <c r="G15" s="14" t="s">
         <v>161</v>
@@ -6310,8 +6340,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="18"/>
       <c r="G16" s="14" t="s">
         <v>138</v>
@@ -6579,11 +6609,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="42"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
       <c r="G2" s="2" t="s">
         <v>76</v>
       </c>
@@ -6598,11 +6628,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="46" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="45"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
       <c r="G3" s="13" t="s">
         <v>78</v>
       </c>
@@ -6640,13 +6670,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="40" t="s">
         <v>186</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="40" t="s">
         <v>180</v>
       </c>
       <c r="G5" s="9" t="s">
@@ -6663,8 +6693,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="18"/>
       <c r="G6" s="15" t="s">
         <v>86</v>
@@ -6680,8 +6710,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
       <c r="D7" s="18"/>
       <c r="G7" s="15" t="s">
         <v>136</v>
@@ -6697,8 +6727,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
       <c r="D8" s="18"/>
       <c r="G8" s="15" t="s">
         <v>103</v>
@@ -6714,8 +6744,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
       <c r="D9" s="18"/>
       <c r="G9" s="15" t="s">
         <v>88</v>
@@ -6731,8 +6761,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
       <c r="D10" s="18"/>
       <c r="G10" s="34" t="s">
         <v>118</v>
@@ -6748,8 +6778,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
       <c r="D11" s="18"/>
       <c r="G11" s="34" t="s">
         <v>166</v>
@@ -6765,8 +6795,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
       <c r="D12" s="18"/>
       <c r="G12" s="15" t="s">
         <v>98</v>
@@ -6782,8 +6812,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
       <c r="D13" s="18"/>
       <c r="G13" s="34" t="s">
         <v>116</v>
@@ -6799,8 +6829,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
       <c r="D14" s="18"/>
       <c r="G14" s="19" t="s">
         <v>127</v>
@@ -6816,8 +6846,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="18"/>
       <c r="G15" s="19" t="s">
         <v>135</v>
@@ -6833,8 +6863,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="18"/>
       <c r="G16" s="19" t="s">
         <v>93</v>
